--- a/Private/DC34_Cnet_Badge_BoMs.xlsx
+++ b/Private/DC34_Cnet_Badge_BoMs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\My Drive\Dev\Arduino\DC34_Cnet_Badge\Private\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90AA0CA9-7810-471D-83E4-475419F3C082}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A6718B2-65E6-428F-A9EA-CB3B4FC52E1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14355" yWindow="2400" windowWidth="27630" windowHeight="17760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15750" yWindow="3450" windowWidth="21135" windowHeight="16245" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DC34_Cnet_Badge" sheetId="1" r:id="rId1"/>
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="52">
   <si>
     <t>Part</t>
   </si>
@@ -90,9 +90,6 @@
     <t>Unit Cost</t>
   </si>
   <si>
-    <t>Total Cost</t>
-  </si>
-  <si>
     <t>Amazon</t>
   </si>
   <si>
@@ -226,6 +223,12 @@
   </si>
   <si>
     <t>RGB LED - Fast Cycle</t>
+  </si>
+  <si>
+    <t>Total BadgeCost</t>
+  </si>
+  <si>
+    <t>Total SAO Cost</t>
   </si>
 </sst>
 </file>
@@ -235,7 +238,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -257,12 +260,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -619,31 +616,31 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C1" t="s">
         <v>4</v>
       </c>
       <c r="D1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H1" t="s">
         <v>40</v>
       </c>
-      <c r="E1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G1" t="s">
-        <v>44</v>
-      </c>
-      <c r="H1" t="s">
-        <v>41</v>
-      </c>
       <c r="I1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -679,7 +676,7 @@
         <v>589.5</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -693,7 +690,7 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -707,7 +704,7 @@
         <v>5.6633333333333331</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F4" s="4">
         <v>3</v>
@@ -720,16 +717,16 @@
         <v>25</v>
       </c>
       <c r="I4" s="2">
-        <f t="shared" ref="I3:I18" si="2">SUM(G4*H4)</f>
+        <f t="shared" ref="I4:I18" si="2">SUM(G4*H4)</f>
         <v>424.74999999999994</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -743,7 +740,7 @@
         <v>1.165</v>
       </c>
       <c r="E5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F5" s="4">
         <v>6</v>
@@ -760,12 +757,12 @@
         <v>90.87</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -779,7 +776,7 @@
         <v>9.49</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F6" s="4">
         <v>2</v>
@@ -796,12 +793,12 @@
         <v>721.24</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -815,7 +812,7 @@
         <v>1.3316666666666668</v>
       </c>
       <c r="E7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F7" s="4">
         <v>6</v>
@@ -832,12 +829,12 @@
         <v>103.87</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B8">
         <v>4</v>
@@ -851,7 +848,7 @@
         <v>1.1996</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F8" s="4">
         <v>100</v>
@@ -868,12 +865,12 @@
         <v>89.97</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B9">
         <v>1</v>
@@ -887,7 +884,7 @@
         <v>1.998</v>
       </c>
       <c r="E9" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F9" s="4">
         <v>5</v>
@@ -904,12 +901,12 @@
         <v>149.85</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B10">
         <v>1</v>
@@ -923,7 +920,7 @@
         <v>4.3979999999999997</v>
       </c>
       <c r="E10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F10" s="4">
         <v>5</v>
@@ -940,12 +937,12 @@
         <v>329.84999999999997</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B11">
         <v>5</v>
@@ -959,7 +956,7 @@
         <v>1.4990000000000001</v>
       </c>
       <c r="E11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F11" s="4">
         <v>50</v>
@@ -976,12 +973,12 @@
         <v>119.92</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B12">
         <v>1</v>
@@ -995,7 +992,7 @@
         <v>6.9900000000000004E-2</v>
       </c>
       <c r="E12" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F12" s="4">
         <v>100</v>
@@ -1012,12 +1009,12 @@
         <v>6.99</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B13">
         <v>1</v>
@@ -1031,7 +1028,7 @@
         <v>6.9900000000000004E-2</v>
       </c>
       <c r="E13" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F13" s="4">
         <v>100</v>
@@ -1048,7 +1045,7 @@
         <v>6.99</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
@@ -1062,7 +1059,7 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B15">
         <v>1</v>
@@ -1076,7 +1073,7 @@
         <v>0.63</v>
       </c>
       <c r="E15" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F15" s="4">
         <v>1</v>
@@ -1093,12 +1090,12 @@
         <v>47.25</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B16">
         <v>1</v>
@@ -1112,7 +1109,7 @@
         <v>1.37</v>
       </c>
       <c r="E16" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F16" s="4">
         <v>1</v>
@@ -1129,12 +1126,12 @@
         <v>102.75000000000001</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B17">
         <v>1</v>
@@ -1148,7 +1145,7 @@
         <v>0.6</v>
       </c>
       <c r="E17" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F17" s="4">
         <v>1</v>
@@ -1165,12 +1162,12 @@
         <v>45</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B18">
         <v>1</v>
@@ -1184,7 +1181,7 @@
         <v>0.53</v>
       </c>
       <c r="E18" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F18" s="4">
         <v>1</v>
@@ -1201,7 +1198,7 @@
         <v>39.75</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
@@ -1216,14 +1213,14 @@
         <v>37.874400000000001</v>
       </c>
       <c r="E21" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I21" s="6">
         <f>SUM(I2:I18)</f>
         <v>2868.5499999999997</v>
       </c>
       <c r="J21" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
@@ -1231,7 +1228,7 @@
         <v>75</v>
       </c>
       <c r="E22" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
@@ -1240,7 +1237,7 @@
         <v>2840.58</v>
       </c>
       <c r="E23" t="s">
-        <v>5</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -1289,31 +1286,31 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C1" t="s">
         <v>4</v>
       </c>
       <c r="D1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H1" t="s">
         <v>40</v>
       </c>
-      <c r="E1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G1" t="s">
-        <v>44</v>
-      </c>
-      <c r="H1" t="s">
-        <v>41</v>
-      </c>
       <c r="I1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -1348,7 +1345,7 @@
         <v>129</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -1362,7 +1359,7 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -1375,7 +1372,7 @@
         <v>0.43</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F4" s="4">
         <v>1</v>
@@ -1392,12 +1389,12 @@
         <v>32.25</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B5">
         <v>2</v>
@@ -1410,7 +1407,7 @@
         <v>1.2</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F5" s="4">
         <v>1</v>
@@ -1427,12 +1424,12 @@
         <v>90</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B6">
         <v>2</v>
@@ -1445,7 +1442,7 @@
         <v>1.2</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F6" s="4">
         <v>1</v>
@@ -1462,12 +1459,12 @@
         <v>90</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -1480,7 +1477,7 @@
         <v>0.17</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F7" s="4">
         <v>1</v>
@@ -1497,7 +1494,7 @@
         <v>12.750000000000002</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -1512,14 +1509,14 @@
         <v>4.72</v>
       </c>
       <c r="E10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I10" s="6">
         <f>SUM(I2:I7)</f>
         <v>354</v>
       </c>
       <c r="J10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
@@ -1527,7 +1524,7 @@
         <v>75</v>
       </c>
       <c r="E11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
@@ -1536,7 +1533,7 @@
         <v>354</v>
       </c>
       <c r="E12" t="s">
-        <v>5</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/Private/DC34_Cnet_Badge_BoMs.xlsx
+++ b/Private/DC34_Cnet_Badge_BoMs.xlsx
@@ -8,13 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\My Drive\Dev\Arduino\DC34_Cnet_Badge\Private\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A6718B2-65E6-428F-A9EA-CB3B4FC52E1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B6A6E7B-E737-4518-8602-9109F1B92C5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15750" yWindow="3450" windowWidth="21135" windowHeight="16245" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15285" yWindow="2085" windowWidth="28155" windowHeight="18390" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DC34_Cnet_Badge" sheetId="1" r:id="rId1"/>
-    <sheet name="DC34_Cnet_SAO" sheetId="3" r:id="rId2"/>
+    <sheet name="DC34_Cnet_Badge - Alt LED" sheetId="5" r:id="rId2"/>
+    <sheet name="DC34_Cnet_SAO" sheetId="3" r:id="rId3"/>
+    <sheet name="DC34_Cnet_SAO - Alt LED" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -57,6 +59,24 @@
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
+    <author>tc={2428E3BB-DB34-4D76-B7A6-FAF80E221492}</author>
+  </authors>
+  <commentList>
+    <comment ref="D2" authorId="0" shapeId="0" xr:uid="{2428E3BB-DB34-4D76-B7A6-FAF80E221492}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    44% Duty &amp; Tax</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
     <author>tc={4EACCE40-934D-4C5B-AFC0-384609DB54BB}</author>
   </authors>
   <commentList>
@@ -72,8 +92,26 @@
 </comments>
 </file>
 
+<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={382ED950-B352-4F40-8692-5916D8FFDE63}</author>
+  </authors>
+  <commentList>
+    <comment ref="D2" authorId="0" shapeId="0" xr:uid="{382ED950-B352-4F40-8692-5916D8FFDE63}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    44% Duty &amp; Tax</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="54">
   <si>
     <t>Part</t>
   </si>
@@ -165,9 +203,6 @@
     <t>https://www.digikey.com/en/products/detail/nidec-components/CL-SB-22C-11/3507850</t>
   </si>
   <si>
-    <t>RGB LED - Slow Cycle</t>
-  </si>
-  <si>
     <t>https://www.digikey.com/en/products/detail/scs/3001012/1621604</t>
   </si>
   <si>
@@ -222,13 +257,22 @@
     <t>Total Order Cost</t>
   </si>
   <si>
-    <t>RGB LED - Fast Cycle</t>
-  </si>
-  <si>
     <t>Total BadgeCost</t>
   </si>
   <si>
     <t>Total SAO Cost</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/sparkfun-electronics/11450/5673784</t>
+  </si>
+  <si>
+    <t>RGB LED - Slow Cycle - 5mm</t>
+  </si>
+  <si>
+    <t>RGB LED - Slow Cycle - 3mm</t>
+  </si>
+  <si>
+    <t>RGB LED - Fast Cycle - 3mm</t>
   </si>
 </sst>
 </file>
@@ -588,7 +632,23 @@
 
 <file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="D2" dT="2026-01-27T17:46:12.02" personId="{9775AD90-BCF0-447F-9730-3B57DA6B0927}" id="{2428E3BB-DB34-4D76-B7A6-FAF80E221492}">
+    <text>44% Duty &amp; Tax</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
+<file path=xl/threadedComments/threadedComment3.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <threadedComment ref="D2" dT="2026-01-27T17:46:12.02" personId="{9775AD90-BCF0-447F-9730-3B57DA6B0927}" id="{4EACCE40-934D-4C5B-AFC0-384609DB54BB}">
+    <text>44% Duty &amp; Tax</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
+<file path=xl/threadedComments/threadedComment4.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="D2" dT="2026-01-27T17:46:12.02" personId="{9775AD90-BCF0-447F-9730-3B57DA6B0927}" id="{382ED950-B352-4F40-8692-5916D8FFDE63}">
     <text>44% Duty &amp; Tax</text>
   </threadedComment>
 </ThreadedComments>
@@ -599,11 +659,11 @@
   <dimension ref="A1:J23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -616,31 +676,31 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C1" t="s">
         <v>4</v>
       </c>
       <c r="D1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H1" t="s">
         <v>39</v>
       </c>
-      <c r="E1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G1" t="s">
-        <v>43</v>
-      </c>
-      <c r="H1" t="s">
-        <v>40</v>
-      </c>
       <c r="I1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -652,11 +712,11 @@
       </c>
       <c r="C2" s="2">
         <f>SUM(G2/F2)</f>
-        <v>7.86</v>
+        <v>9.6893333333333338</v>
       </c>
       <c r="D2" s="2">
         <f>SUM(C2*B2)</f>
-        <v>7.86</v>
+        <v>9.6893333333333338</v>
       </c>
       <c r="E2" t="s">
         <v>3</v>
@@ -665,15 +725,15 @@
         <v>1</v>
       </c>
       <c r="G2" s="2">
-        <v>7.86</v>
+        <f>SUM(I2/H2)</f>
+        <v>9.6893333333333338</v>
       </c>
       <c r="H2" s="5">
         <f>ROUNDUP(SUM(B2*D22/F2), 0)</f>
         <v>75</v>
       </c>
       <c r="I2" s="2">
-        <f>SUM(G2*H2)</f>
-        <v>589.5</v>
+        <v>726.7</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>6</v>
@@ -793,7 +853,7 @@
         <v>721.24</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -829,7 +889,7 @@
         <v>103.87</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -865,7 +925,7 @@
         <v>89.97</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -901,7 +961,7 @@
         <v>149.85</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -937,7 +997,7 @@
         <v>329.84999999999997</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
@@ -1009,12 +1069,12 @@
         <v>6.99</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B13">
         <v>1</v>
@@ -1045,7 +1105,7 @@
         <v>6.99</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
@@ -1131,7 +1191,7 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="B17">
         <v>1</v>
@@ -1198,7 +1258,7 @@
         <v>39.75</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
@@ -1210,17 +1270,17 @@
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D21" s="2">
         <f>SUM(D2:D18)</f>
-        <v>37.874400000000001</v>
+        <v>39.703733333333332</v>
       </c>
       <c r="E21" t="s">
         <v>12</v>
       </c>
       <c r="I21" s="6">
         <f>SUM(I2:I18)</f>
-        <v>2868.5499999999997</v>
+        <v>3005.7499999999995</v>
       </c>
       <c r="J21" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
@@ -1228,16 +1288,16 @@
         <v>75</v>
       </c>
       <c r="E22" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D23" s="2">
         <f>SUM(D21*D22)</f>
-        <v>2840.58</v>
+        <v>2977.7799999999997</v>
       </c>
       <c r="E23" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -1265,11 +1325,680 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D52ED08F-CDB2-4095-92B7-15AD2026A4C2}">
+  <dimension ref="A1:J23"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H1" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2">
+        <f>SUM(G2/F2)</f>
+        <v>7.86</v>
+      </c>
+      <c r="D2" s="2">
+        <f>SUM(C2*B2)</f>
+        <v>7.86</v>
+      </c>
+      <c r="E2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="4">
+        <v>1</v>
+      </c>
+      <c r="G2" s="2">
+        <v>7.86</v>
+      </c>
+      <c r="H2" s="5">
+        <f>ROUNDUP(SUM(B2*D22/F2), 0)</f>
+        <v>75</v>
+      </c>
+      <c r="I2" s="2">
+        <v>726.7</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="3"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4" s="2">
+        <f t="shared" ref="C4:C13" si="0">SUM(G4/F4)</f>
+        <v>5.6633333333333331</v>
+      </c>
+      <c r="D4" s="2">
+        <f t="shared" ref="D4:D13" si="1">SUM(C4*B4)</f>
+        <v>5.6633333333333331</v>
+      </c>
+      <c r="E4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F4" s="4">
+        <v>3</v>
+      </c>
+      <c r="G4" s="2">
+        <v>16.989999999999998</v>
+      </c>
+      <c r="H4" s="5">
+        <f>ROUNDUP(SUM(B4*D22/F4), 0)</f>
+        <v>25</v>
+      </c>
+      <c r="I4" s="2">
+        <f t="shared" ref="I4:I18" si="2">SUM(G4*H4)</f>
+        <v>424.74999999999994</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5" s="2">
+        <f t="shared" si="0"/>
+        <v>1.165</v>
+      </c>
+      <c r="D5" s="2">
+        <f t="shared" si="1"/>
+        <v>1.165</v>
+      </c>
+      <c r="E5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F5" s="4">
+        <v>6</v>
+      </c>
+      <c r="G5" s="2">
+        <v>6.99</v>
+      </c>
+      <c r="H5" s="5">
+        <f>ROUNDUP(SUM(B5*D22/F5), 0)</f>
+        <v>13</v>
+      </c>
+      <c r="I5" s="2">
+        <f t="shared" si="2"/>
+        <v>90.87</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6" s="2">
+        <f t="shared" si="0"/>
+        <v>9.49</v>
+      </c>
+      <c r="D6" s="2">
+        <f t="shared" si="1"/>
+        <v>9.49</v>
+      </c>
+      <c r="E6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F6" s="4">
+        <v>2</v>
+      </c>
+      <c r="G6" s="2">
+        <v>18.98</v>
+      </c>
+      <c r="H6" s="5">
+        <f>ROUNDUP(SUM(B6*D22/F6), 0)</f>
+        <v>38</v>
+      </c>
+      <c r="I6" s="2">
+        <f t="shared" si="2"/>
+        <v>721.24</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7" s="2">
+        <f t="shared" si="0"/>
+        <v>1.3316666666666668</v>
+      </c>
+      <c r="D7" s="2">
+        <f t="shared" si="1"/>
+        <v>1.3316666666666668</v>
+      </c>
+      <c r="E7" t="s">
+        <v>5</v>
+      </c>
+      <c r="F7" s="4">
+        <v>6</v>
+      </c>
+      <c r="G7" s="2">
+        <v>7.99</v>
+      </c>
+      <c r="H7" s="5">
+        <f>ROUNDUP(SUM(B7*D22/F7), 0)</f>
+        <v>13</v>
+      </c>
+      <c r="I7" s="2">
+        <f t="shared" si="2"/>
+        <v>103.87</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8">
+        <v>4</v>
+      </c>
+      <c r="C8" s="2">
+        <f t="shared" si="0"/>
+        <v>0.2999</v>
+      </c>
+      <c r="D8" s="2">
+        <f t="shared" si="1"/>
+        <v>1.1996</v>
+      </c>
+      <c r="E8" t="s">
+        <v>5</v>
+      </c>
+      <c r="F8" s="4">
+        <v>100</v>
+      </c>
+      <c r="G8" s="2">
+        <v>29.99</v>
+      </c>
+      <c r="H8" s="5">
+        <f>ROUNDUP(SUM(B8*D22/F8), 0)</f>
+        <v>3</v>
+      </c>
+      <c r="I8" s="2">
+        <f t="shared" si="2"/>
+        <v>89.97</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9" s="2">
+        <f t="shared" si="0"/>
+        <v>1.998</v>
+      </c>
+      <c r="D9" s="2">
+        <f t="shared" si="1"/>
+        <v>1.998</v>
+      </c>
+      <c r="E9" t="s">
+        <v>5</v>
+      </c>
+      <c r="F9" s="4">
+        <v>5</v>
+      </c>
+      <c r="G9" s="2">
+        <v>9.99</v>
+      </c>
+      <c r="H9" s="5">
+        <f>ROUNDUP(SUM(B9*D22/F9), 0)</f>
+        <v>15</v>
+      </c>
+      <c r="I9" s="2">
+        <f t="shared" si="2"/>
+        <v>149.85</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10" s="2">
+        <f t="shared" si="0"/>
+        <v>4.3979999999999997</v>
+      </c>
+      <c r="D10" s="2">
+        <f t="shared" si="1"/>
+        <v>4.3979999999999997</v>
+      </c>
+      <c r="E10" t="s">
+        <v>5</v>
+      </c>
+      <c r="F10" s="4">
+        <v>5</v>
+      </c>
+      <c r="G10" s="2">
+        <v>21.99</v>
+      </c>
+      <c r="H10" s="5">
+        <f>ROUNDUP(SUM(B10*D22/F10), 0)</f>
+        <v>15</v>
+      </c>
+      <c r="I10" s="2">
+        <f t="shared" si="2"/>
+        <v>329.84999999999997</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11">
+        <v>5</v>
+      </c>
+      <c r="C11" s="2">
+        <f t="shared" si="0"/>
+        <v>0.29980000000000001</v>
+      </c>
+      <c r="D11" s="2">
+        <f t="shared" si="1"/>
+        <v>1.4990000000000001</v>
+      </c>
+      <c r="E11" t="s">
+        <v>5</v>
+      </c>
+      <c r="F11" s="4">
+        <v>50</v>
+      </c>
+      <c r="G11" s="2">
+        <v>14.99</v>
+      </c>
+      <c r="H11" s="5">
+        <f>ROUNDUP(SUM(B11*D22/F11), 0)</f>
+        <v>8</v>
+      </c>
+      <c r="I11" s="2">
+        <f t="shared" si="2"/>
+        <v>119.92</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12" s="2">
+        <f t="shared" si="0"/>
+        <v>6.9900000000000004E-2</v>
+      </c>
+      <c r="D12" s="2">
+        <f t="shared" si="1"/>
+        <v>6.9900000000000004E-2</v>
+      </c>
+      <c r="E12" t="s">
+        <v>5</v>
+      </c>
+      <c r="F12" s="4">
+        <v>100</v>
+      </c>
+      <c r="G12" s="2">
+        <v>6.99</v>
+      </c>
+      <c r="H12" s="5">
+        <f>ROUNDUP(SUM(B12*D22/F12), 0)</f>
+        <v>1</v>
+      </c>
+      <c r="I12" s="2">
+        <f t="shared" si="2"/>
+        <v>6.99</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13" s="2">
+        <f t="shared" si="0"/>
+        <v>6.9900000000000004E-2</v>
+      </c>
+      <c r="D13" s="2">
+        <f t="shared" si="1"/>
+        <v>6.9900000000000004E-2</v>
+      </c>
+      <c r="E13" t="s">
+        <v>5</v>
+      </c>
+      <c r="F13" s="4">
+        <v>100</v>
+      </c>
+      <c r="G13" s="2">
+        <v>6.99</v>
+      </c>
+      <c r="H13" s="5">
+        <f>ROUNDUP(SUM(B13*D22/F13), 0)</f>
+        <v>1</v>
+      </c>
+      <c r="I13" s="2">
+        <f t="shared" si="2"/>
+        <v>6.99</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="1"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>7</v>
+      </c>
+      <c r="B15">
+        <v>1</v>
+      </c>
+      <c r="C15" s="2">
+        <f>SUM(G15/F15)</f>
+        <v>0.63</v>
+      </c>
+      <c r="D15" s="2">
+        <f>SUM(C15*B15)</f>
+        <v>0.63</v>
+      </c>
+      <c r="E15" t="s">
+        <v>9</v>
+      </c>
+      <c r="F15" s="4">
+        <v>1</v>
+      </c>
+      <c r="G15" s="2">
+        <v>0.63</v>
+      </c>
+      <c r="H15" s="5">
+        <f>ROUNDUP(SUM(B15*D22/F15), 0)</f>
+        <v>75</v>
+      </c>
+      <c r="I15" s="2">
+        <f t="shared" si="2"/>
+        <v>47.25</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>11</v>
+      </c>
+      <c r="B16">
+        <v>1</v>
+      </c>
+      <c r="C16" s="2">
+        <f>SUM(G16/F16)</f>
+        <v>1.37</v>
+      </c>
+      <c r="D16" s="2">
+        <f>SUM(C16*B16)</f>
+        <v>1.37</v>
+      </c>
+      <c r="E16" t="s">
+        <v>9</v>
+      </c>
+      <c r="F16" s="4">
+        <v>1</v>
+      </c>
+      <c r="G16" s="2">
+        <v>1.37</v>
+      </c>
+      <c r="H16" s="5">
+        <f>ROUNDUP(SUM(B16*D22/F16), 0)</f>
+        <v>75</v>
+      </c>
+      <c r="I16" s="2">
+        <f t="shared" si="2"/>
+        <v>102.75000000000001</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>51</v>
+      </c>
+      <c r="B17">
+        <v>1</v>
+      </c>
+      <c r="C17" s="2">
+        <f>SUM(G17/F17)</f>
+        <v>0.99</v>
+      </c>
+      <c r="D17" s="2">
+        <f>SUM(C17*B17)</f>
+        <v>0.99</v>
+      </c>
+      <c r="E17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F17" s="4">
+        <v>1</v>
+      </c>
+      <c r="G17" s="2">
+        <v>0.99</v>
+      </c>
+      <c r="H17" s="5">
+        <f>ROUNDUP(SUM(B17*D22/F17), 0)</f>
+        <v>75</v>
+      </c>
+      <c r="I17" s="2">
+        <f t="shared" si="2"/>
+        <v>74.25</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>10</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18" s="2">
+        <f>SUM(G18/F18)</f>
+        <v>0.53</v>
+      </c>
+      <c r="D18" s="2">
+        <f>SUM(C18*B18)</f>
+        <v>0.53</v>
+      </c>
+      <c r="E18" t="s">
+        <v>9</v>
+      </c>
+      <c r="F18" s="4">
+        <v>1</v>
+      </c>
+      <c r="G18" s="2">
+        <v>0.53</v>
+      </c>
+      <c r="H18" s="5">
+        <f>ROUNDUP(SUM(B18*D22/F18), 0)</f>
+        <v>75</v>
+      </c>
+      <c r="I18" s="2">
+        <f t="shared" si="2"/>
+        <v>39.75</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D21" s="2">
+        <f>SUM(D2:D18)</f>
+        <v>38.264400000000002</v>
+      </c>
+      <c r="E21" t="s">
+        <v>12</v>
+      </c>
+      <c r="I21" s="6">
+        <f>SUM(I2:I18)</f>
+        <v>3034.9999999999995</v>
+      </c>
+      <c r="J21" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D22">
+        <v>75</v>
+      </c>
+      <c r="E22" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D23" s="2">
+        <f>SUM(D21*D22)</f>
+        <v>2869.83</v>
+      </c>
+      <c r="E23" t="s">
+        <v>48</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="J2" r:id="rId1" xr:uid="{C4182A51-B2A8-416C-943F-5A46A35835F6}"/>
+    <hyperlink ref="J4" r:id="rId2" xr:uid="{C8DCA1ED-12D9-47D0-92E1-8080DB14EAB3}"/>
+    <hyperlink ref="J5" r:id="rId3" xr:uid="{382B1B69-7C5F-4468-94F8-2882C993F583}"/>
+    <hyperlink ref="J6" r:id="rId4" xr:uid="{4EDED880-A4DC-4A5A-AE0F-9D7F0D3F7816}"/>
+    <hyperlink ref="J9" r:id="rId5" xr:uid="{2DC8603D-0A89-47B6-9EF2-68EB9DB2CF56}"/>
+    <hyperlink ref="J10" r:id="rId6" xr:uid="{FE97F6E4-014C-410F-A917-17CD2325A979}"/>
+    <hyperlink ref="J11" r:id="rId7" xr:uid="{DE382ADA-A750-43C7-B4BE-616209CC2D6D}"/>
+    <hyperlink ref="J15" r:id="rId8" xr:uid="{9FB952BC-4F34-4F6E-8919-360CD0350233}"/>
+    <hyperlink ref="J17" r:id="rId9" xr:uid="{6F5AD1C6-0744-4F99-AF78-2C7D6BC904A3}"/>
+    <hyperlink ref="J18" r:id="rId10" xr:uid="{56619F22-28E5-49CC-9058-191172A4EF2C}"/>
+    <hyperlink ref="J12" r:id="rId11" xr:uid="{2CEBCE69-E65D-4452-B0A6-DAC1A0034997}"/>
+    <hyperlink ref="J16" r:id="rId12" xr:uid="{6541C708-61D8-4B52-9137-CE62F128F582}"/>
+    <hyperlink ref="J8" r:id="rId13" xr:uid="{074C46C4-1604-4442-A877-DBFD9B61D716}"/>
+    <hyperlink ref="J7" r:id="rId14" xr:uid="{08460866-EE24-4DDE-A4B0-FB9692FADCAB}"/>
+    <hyperlink ref="J13" r:id="rId15" xr:uid="{2160EF5F-78DE-432E-8257-85922D292B1F}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId16"/>
+  <legacyDrawing r:id="rId17"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4518F86-BB93-46FA-9760-3566465D3B5D}">
   <dimension ref="A1:J12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.85546875" bestFit="1" customWidth="1"/>
@@ -1286,31 +2015,31 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C1" t="s">
         <v>4</v>
       </c>
       <c r="D1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H1" t="s">
         <v>39</v>
       </c>
-      <c r="E1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G1" t="s">
-        <v>43</v>
-      </c>
-      <c r="H1" t="s">
-        <v>40</v>
-      </c>
       <c r="I1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -1321,11 +2050,12 @@
         <v>1</v>
       </c>
       <c r="C2" s="2">
-        <v>1.72</v>
+        <f>SUM(G2/F2)</f>
+        <v>1.2036</v>
       </c>
       <c r="D2" s="2">
         <f>SUM(C2*B2)</f>
-        <v>1.72</v>
+        <v>1.2036</v>
       </c>
       <c r="E2" t="s">
         <v>3</v>
@@ -1334,15 +2064,15 @@
         <v>1</v>
       </c>
       <c r="G2" s="2">
-        <v>1.72</v>
+        <f>SUM(I2/H2)</f>
+        <v>1.2036</v>
       </c>
       <c r="H2" s="5">
         <f>ROUNDUP(SUM(B2*D11/F2), 0)</f>
         <v>75</v>
       </c>
       <c r="I2" s="2">
-        <f>SUM(G2*H2)</f>
-        <v>129</v>
+        <v>90.27</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>6</v>
@@ -1365,6 +2095,7 @@
         <v>1</v>
       </c>
       <c r="C4" s="2">
+        <f t="shared" ref="C4:C7" si="0">SUM(G4/F4)</f>
         <v>0.43</v>
       </c>
       <c r="D4" s="2">
@@ -1385,7 +2116,7 @@
         <v>75</v>
       </c>
       <c r="I4" s="2">
-        <f t="shared" ref="I4:I7" si="0">SUM(G4*H4)</f>
+        <f t="shared" ref="I4:I7" si="1">SUM(G4*H4)</f>
         <v>32.25</v>
       </c>
       <c r="J4" s="1" t="s">
@@ -1394,12 +2125,13 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="B5">
         <v>2</v>
       </c>
       <c r="C5" s="2">
+        <f t="shared" si="0"/>
         <v>0.6</v>
       </c>
       <c r="D5" s="2">
@@ -1420,7 +2152,7 @@
         <v>150</v>
       </c>
       <c r="I5" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>90</v>
       </c>
       <c r="J5" s="1" t="s">
@@ -1429,12 +2161,13 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B6">
         <v>2</v>
       </c>
       <c r="C6" s="2">
+        <f t="shared" si="0"/>
         <v>0.6</v>
       </c>
       <c r="D6" s="2">
@@ -1455,7 +2188,7 @@
         <v>150</v>
       </c>
       <c r="I6" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>90</v>
       </c>
       <c r="J6" s="1" t="s">
@@ -1470,6 +2203,7 @@
         <v>1</v>
       </c>
       <c r="C7" s="2">
+        <f t="shared" si="0"/>
         <v>0.17</v>
       </c>
       <c r="D7" s="2">
@@ -1490,7 +2224,7 @@
         <v>75</v>
       </c>
       <c r="I7" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>12.750000000000002</v>
       </c>
       <c r="J7" s="1" t="s">
@@ -1506,17 +2240,17 @@
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D10" s="2">
         <f>SUM(D2:D7)</f>
-        <v>4.72</v>
+        <v>4.2035999999999998</v>
       </c>
       <c r="E10" t="s">
         <v>12</v>
       </c>
       <c r="I10" s="6">
         <f>SUM(I2:I7)</f>
-        <v>354</v>
+        <v>315.27</v>
       </c>
       <c r="J10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
@@ -1524,16 +2258,16 @@
         <v>75</v>
       </c>
       <c r="E11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D12" s="2">
         <f>SUM(D10*D11)</f>
-        <v>354</v>
+        <v>315.27</v>
       </c>
       <c r="E12" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -1550,6 +2284,260 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1296A6D4-0EE0-4E2D-8C6F-AC051B356080}">
+  <dimension ref="A1:J11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="86.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H1" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2">
+        <f>SUM(G2/F2)</f>
+        <v>1.2036</v>
+      </c>
+      <c r="D2" s="2">
+        <f>SUM(C2*B2)</f>
+        <v>1.2036</v>
+      </c>
+      <c r="E2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="4">
+        <v>1</v>
+      </c>
+      <c r="G2" s="2">
+        <f>SUM(I2/H2)</f>
+        <v>1.2036</v>
+      </c>
+      <c r="H2" s="5">
+        <f>ROUNDUP(SUM(B2*D10/F2), 0)</f>
+        <v>75</v>
+      </c>
+      <c r="I2" s="2">
+        <v>90.27</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="3"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4" s="2">
+        <f>SUM(G4/F4)</f>
+        <v>0.43</v>
+      </c>
+      <c r="D4" s="2">
+        <f>SUM(C4*B4)</f>
+        <v>0.43</v>
+      </c>
+      <c r="E4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="4">
+        <v>1</v>
+      </c>
+      <c r="G4" s="2">
+        <v>0.43</v>
+      </c>
+      <c r="H4" s="5">
+        <f>ROUNDUP(SUM(B4*D10/F4), 0)</f>
+        <v>75</v>
+      </c>
+      <c r="I4" s="2">
+        <f t="shared" ref="I4:I6" si="0">SUM(G4*H4)</f>
+        <v>32.25</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5" s="2">
+        <f t="shared" ref="C5:C6" si="1">SUM(G5/F5)</f>
+        <v>0.99</v>
+      </c>
+      <c r="D5" s="2">
+        <f>SUM(C5*B5)</f>
+        <v>3.96</v>
+      </c>
+      <c r="E5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="4">
+        <v>1</v>
+      </c>
+      <c r="G5" s="2">
+        <v>0.99</v>
+      </c>
+      <c r="H5" s="5">
+        <f>ROUNDUP(SUM(B5*D10/F5), 0)</f>
+        <v>300</v>
+      </c>
+      <c r="I5" s="2">
+        <f t="shared" si="0"/>
+        <v>297</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6" s="2">
+        <f t="shared" si="1"/>
+        <v>0.17</v>
+      </c>
+      <c r="D6" s="2">
+        <f>SUM(C6*B6)</f>
+        <v>0.17</v>
+      </c>
+      <c r="E6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" s="4">
+        <v>1</v>
+      </c>
+      <c r="G6" s="2">
+        <v>0.17</v>
+      </c>
+      <c r="H6" s="5">
+        <f>ROUNDUP(SUM(B6*D10/F6), 0)</f>
+        <v>75</v>
+      </c>
+      <c r="I6" s="2">
+        <f t="shared" si="0"/>
+        <v>12.750000000000002</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D9" s="2">
+        <f>SUM(D2:D6)</f>
+        <v>5.7636000000000003</v>
+      </c>
+      <c r="E9" t="s">
+        <v>12</v>
+      </c>
+      <c r="I9" s="6">
+        <f>SUM(I2:I6)</f>
+        <v>432.27</v>
+      </c>
+      <c r="J9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D10">
+        <v>75</v>
+      </c>
+      <c r="E10" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D11" s="2">
+        <f>SUM(D9*D10)</f>
+        <v>432.27000000000004</v>
+      </c>
+      <c r="E11" t="s">
+        <v>49</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="J2" r:id="rId1" xr:uid="{4843F101-C014-4A51-840F-75CD8885FD91}"/>
+    <hyperlink ref="J4" r:id="rId2" xr:uid="{2310D023-2E13-432F-A344-A9BAB145F1E7}"/>
+    <hyperlink ref="J6" r:id="rId3" xr:uid="{CCCCAB3A-252D-4947-AA69-A73893B9960F}"/>
+    <hyperlink ref="J5" r:id="rId4" xr:uid="{8BDB17D9-837C-4D72-BFBA-0216972E3986}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId5"/>
+  <legacyDrawing r:id="rId6"/>
+</worksheet>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{aed08b9e-6013-4d94-8247-03aa66eb0c6a}" enabled="1" method="Standard" siteId="{d4d76e39-e33d-45e4-835c-f6f4f74b5560}" contentBits="0" removed="0"/>
